--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:20</t>
+    <t xml:space="preserve">2026-09-09 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -62,12 +62,12 @@
     <t xml:space="preserve">Promedio Regional</t>
   </si>
   <si>
+    <t xml:space="preserve">Marga Marga</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Marga Marga</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:19</t>
+    <t xml:space="preserve">2026-09-17 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -809,16 +809,16 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5.92</v>
+        <v>5.74</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12.12</v>
+        <v>9.13</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -832,16 +832,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>31.51</v>
+        <v>26.42</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -858,13 +858,13 @@
         <v>5.26</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4.32</v>
+        <v>4.48</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.94</v>
+        <v>0.78</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21.76</v>
+        <v>17.41</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -878,16 +878,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5.74</v>
+        <v>5.92</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>9.13</v>
+        <v>12.12</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -901,16 +901,16 @@
         <v>9</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>26.42</v>
+        <v>31.51</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -927,13 +927,13 @@
         <v>5.26</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4.48</v>
+        <v>4.32</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.78</v>
+        <v>0.94</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>17.41</v>
+        <v>21.76</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.58</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="4">
@@ -1283,7 +1283,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>5.26</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.02</v>
+        <v>5.26</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.48</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.06</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7.09</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5.16</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.7</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.58</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="11">
@@ -1525,7 +1525,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>35</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>36</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>32</v>
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4.17</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5.02</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:45</t>
+    <t xml:space="preserve">2026-09-25 21:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -542,7 +542,7 @@
         <v>0.96</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>19.39</v>
+        <v>19.35</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>9</v>
@@ -562,10 +562,10 @@
         <v>2.86</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.37</v>
+        <v>29.02</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>9</v>
@@ -585,10 +585,10 @@
         <v>3.7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23.78</v>
+        <v>23.59</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>9</v>
@@ -611,7 +611,7 @@
         <v>0.75</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14.37</v>
+        <v>14.47</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>8</v>
@@ -634,7 +634,7 @@
         <v>0.92</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27.71</v>
+        <v>27.8</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8</v>
@@ -657,7 +657,7 @@
         <v>0.85</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>20.38</v>
+        <v>20.41</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8</v>
@@ -680,7 +680,7 @@
         <v>0.58</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10.34</v>
+        <v>10.31</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>7</v>
@@ -703,7 +703,7 @@
         <v>0.91</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>24.66</v>
+        <v>24.7</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7</v>
@@ -726,7 +726,7 @@
         <v>0.77</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>17.23</v>
+        <v>17.19</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7</v>
@@ -749,7 +749,7 @@
         <v>0.72</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>13.51</v>
+        <v>13.44</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>6</v>
@@ -769,10 +769,10 @@
         <v>3.64</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>27.75</v>
+        <v>27.92</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6</v>
@@ -792,10 +792,10 @@
         <v>4.37</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>20.37</v>
+        <v>20.22</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>6</v>
@@ -818,7 +818,7 @@
         <v>0.48</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9.13</v>
+        <v>9.16</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -841,7 +841,7 @@
         <v>1.02</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>26.42</v>
+        <v>26.41</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -864,7 +864,7 @@
         <v>0.78</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>17.41</v>
+        <v>17.37</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
         <v>5.28</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>12.12</v>
+        <v>12.27</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -910,7 +910,7 @@
         <v>1.15</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>31.51</v>
+        <v>31.59</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -933,7 +933,7 @@
         <v>0.94</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>21.76</v>
+        <v>21.8</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>
@@ -956,7 +956,7 @@
         <v>0.94</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>16.32</v>
+        <v>16.35</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3</v>
@@ -976,10 +976,10 @@
         <v>4.59</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>28.32</v>
+        <v>28.51</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3</v>
@@ -1002,7 +1002,7 @@
         <v>1.15</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>22.59</v>
+        <v>22.54</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -1025,7 +1025,7 @@
         <v>0.91</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>15.19</v>
+        <v>15.23</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2</v>
@@ -1045,10 +1045,10 @@
         <v>4.51</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>30.6</v>
+        <v>30.45</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2</v>
@@ -1071,7 +1071,7 @@
         <v>1.17</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>22.81</v>
+        <v>22.9</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>2</v>
@@ -1094,7 +1094,7 @@
         <v>2.1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>43.93</v>
+        <v>43.89</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>1.97</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>36.89</v>
+        <v>36.91</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>5.06</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>40.12</v>
+        <v>40.27</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:41</t>
+    <t xml:space="preserve">2026-10-05 07:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
